--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,51 +782,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96117276</v>
+        <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87156</v>
+        <v>87376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Juvelspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius croceocaeruleus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skäftekärr S, bokhultet, Öl</t>
+          <t>Saxmossen, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620153</v>
+        <v>620143</v>
       </c>
       <c r="R3" t="n">
-        <v>6346030</v>
+        <v>6346062</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,81 +878,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Martin Peraic</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Mikael Jeppson</t>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117276</t>
+          <t>https://artportalen.se/Sighting/137115600</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129352702</v>
+        <v>96117276</v>
       </c>
       <c r="B4" t="n">
-        <v>91897</v>
+        <v>87156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>881</v>
+        <v>444</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skillerticka</t>
+          <t>Juvelspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inonotus cuticularis</t>
+          <t>Cortinarius croceocaeruleus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
+          <t>(Pers. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Skäftekärr S, bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620074</v>
+        <v>620153</v>
       </c>
       <c r="R4" t="n">
-        <v>6346087</v>
+        <v>6346030</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,80 +984,81 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Tommy Knutsson, Mikael Jeppson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352702</t>
+          <t>https://artportalen.se/Sighting/96117276</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129352638</v>
+        <v>129352702</v>
       </c>
       <c r="B5" t="n">
-        <v>90639</v>
+        <v>91897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>970</v>
+        <v>881</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Skillerticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Inonotus cuticularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620082</v>
+        <v>620074</v>
       </c>
       <c r="R5" t="n">
-        <v>6346069</v>
+        <v>6346087</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,54 +1113,63 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352638</t>
+          <t>https://artportalen.se/Sighting/129352702</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>314963</v>
+        <v>129352638</v>
       </c>
       <c r="B6" t="n">
-        <v>90637</v>
+        <v>90639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brödmusseron</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucopaxillus tricolor</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Kühner</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 km SV Skäftekärr, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620156</v>
+        <v>620082</v>
       </c>
       <c r="R6" t="n">
-        <v>6346073</v>
+        <v>6346069</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-08-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-08-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,28 +1210,27 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bokskog vid bruksväg</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Vera Wendt, Göran Wendt</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/314963</t>
+          <t>https://artportalen.se/Sighting/129352638</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>314964</v>
+        <v>314963</v>
       </c>
       <c r="B7" t="n">
         <v>90637</v>
@@ -1244,17 +1261,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>1 km SV Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620164</v>
+        <v>620156</v>
       </c>
       <c r="R7" t="n">
-        <v>6346086</v>
+        <v>6346073</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,12 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2010-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2010-08-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,30 +1314,26 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>bokskog vid kanal</t>
-        </is>
-      </c>
+          <t>Bokskog vid bruksväg</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
+          <t>Vera Wendt, Göran Wendt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/314964</t>
+          <t>https://artportalen.se/Sighting/314963</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96117414</v>
+        <v>314964</v>
       </c>
       <c r="B8" t="n">
         <v>90637</v>
@@ -1349,19 +1362,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftekärr S, bokhultet, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620153</v>
+        <v>620164</v>
       </c>
       <c r="R8" t="n">
-        <v>6346030</v>
+        <v>6346086</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,12 +1398,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,65 +1412,60 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+          <t>bokskog vid kanal</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Mikael Jeppson</t>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117414</t>
+          <t>https://artportalen.se/Sighting/314964</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96117342</v>
+        <v>96117414</v>
       </c>
       <c r="B9" t="n">
-        <v>87375</v>
+        <v>90637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3739</v>
+        <v>974</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Brödmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Leucopaxillus tricolor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Peck) Kühner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,7 +1522,11 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,51 +1549,58 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96117342</t>
+          <t>https://artportalen.se/Sighting/96117414</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129352715</v>
+        <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87375</v>
+        <v>87373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3739</v>
+        <v>1978</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Silverfotsspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius argenteolilacinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Saxmossen, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620116</v>
+        <v>620149</v>
       </c>
       <c r="R10" t="n">
-        <v>6346113</v>
+        <v>6346040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,12 +1627,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,55 +1651,56 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Martin Peraic</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352715</t>
+          <t>https://artportalen.se/Sighting/137116492</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96118549</v>
+        <v>96117342</v>
       </c>
       <c r="B11" t="n">
-        <v>91322</v>
+        <v>87375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4188</v>
+        <v>3739</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,54 +1780,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96118549</t>
+          <t>https://artportalen.se/Sighting/96117342</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2157760</v>
+        <v>129352715</v>
       </c>
       <c r="B12" t="n">
-        <v>111175</v>
+        <v>87375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>3739</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620164</v>
+        <v>620116</v>
       </c>
       <c r="R12" t="n">
-        <v>6346086</v>
+        <v>6346113</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,12 +1851,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,40 +1867,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2157760</t>
+          <t>https://artportalen.se/Sighting/129352715</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>59519824</v>
+        <v>96118549</v>
       </c>
       <c r="B13" t="n">
-        <v>111175</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,37 +1899,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219677</v>
+        <v>4188</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>bokskogen, Öl</t>
+          <t>Skäftekärr S, bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620154</v>
+        <v>620153</v>
       </c>
       <c r="R13" t="n">
-        <v>6346064</v>
+        <v>6346030</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1938,12 +1956,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-05-07</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-05-07</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,72 +1970,81 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Bokskogshult med äldre bok, ädelgran, weymouthtall kring kanal</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson, Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59519824</t>
+          <t>https://artportalen.se/Sighting/96118549</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135208553</v>
+        <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>99251</v>
+        <v>93452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219797</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Saxmossen, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620026</v>
+        <v>620135</v>
       </c>
       <c r="R14" t="n">
-        <v>6346219</v>
+        <v>6346036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,17 +2071,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 ex i knopp 1 m från beläggningskanten</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,37 +2095,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Martin Peraic</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135208553</t>
+          <t>https://artportalen.se/Sighting/137115228</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135208554</v>
+        <v>2157760</v>
       </c>
       <c r="B15" t="n">
-        <v>99251</v>
+        <v>111175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,37 +2130,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219797</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620042</v>
+        <v>620164</v>
       </c>
       <c r="R15" t="n">
-        <v>6346234</v>
+        <v>6346086</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2155,17 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 ex i knopp 1 m från beläggningskanten</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,35 +2200,40 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135208554</t>
+          <t>https://artportalen.se/Sighting/2157760</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2925640</v>
+        <v>59519824</v>
       </c>
       <c r="B16" t="n">
-        <v>99096</v>
+        <v>111175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,39 +2241,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>bokskogen, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620164</v>
+        <v>620154</v>
       </c>
       <c r="R16" t="n">
-        <v>6346086</v>
+        <v>6346064</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,12 +2298,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2016-05-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2016-05-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,21 +2314,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Teresa Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+          <t>Teresa Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2311,16 +2333,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2925640</t>
+          <t>https://artportalen.se/Sighting/59519824</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4945457</v>
+        <v>135208553</v>
       </c>
       <c r="B17" t="n">
-        <v>101325</v>
+        <v>99251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,37 +2350,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bokhultet syd Skäftekärr, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620151</v>
+        <v>620026</v>
       </c>
       <c r="R17" t="n">
-        <v>6346042</v>
+        <v>6346219</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,12 +2404,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,75 +2425,70 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>bokskog vid kanal</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4945457</t>
+          <t>https://artportalen.se/Sighting/135208553</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129352710</v>
+        <v>135208554</v>
       </c>
       <c r="B18" t="n">
-        <v>87204</v>
+        <v>99251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248952</v>
+        <v>219797</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620142</v>
+        <v>620042</v>
       </c>
       <c r="R18" t="n">
-        <v>6346007</v>
+        <v>6346234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,12 +2515,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 ex i knopp 1 m från beläggningskanten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,65 +2540,74 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Julien Hach</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352710</t>
+          <t>https://artportalen.se/Sighting/135208554</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129540854</v>
+        <v>2925640</v>
       </c>
       <c r="B19" t="n">
-        <v>87262</v>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>248956</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620133</v>
+        <v>620164</v>
       </c>
       <c r="R19" t="n">
-        <v>6346064</v>
+        <v>6346086</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2595,12 +2631,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,29 +2645,833 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Ingrid Johnsson, Håkan Lundkvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2925640</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4945457</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bokhultet syd Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>620151</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6346042</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-08-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>bokskog vid kanal</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson, Jan-Olof Petersson, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4945457</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137115221</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87405</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>248930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallkejsarspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius cedretorum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Maire</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>620131</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6346033</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137115221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129352710</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87204</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620142</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6346007</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Julien Hach</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Julien Hach, Karin Hjelmér</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129352710</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129540854</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Byrum, Byrum, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6346064</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Julien Hach</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Julien Hach, Martin Peraic</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129540854</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137115511</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87445</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>620130</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6346049</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137115511</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137127987</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87506</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>620130</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6346049</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137127987</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137127949</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87557</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>620130</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6346057</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137127949</t>
         </is>
       </c>
     </row>
@@ -2655,6 +3495,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87373</v>
+        <v>87379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87405</v>
+        <v>87411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,48 +2908,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129352710</v>
+        <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87204</v>
+        <v>87411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248952</v>
+        <v>248930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Tallkejsarspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius cedretorum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Maire</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620142</v>
+        <v>620123</v>
       </c>
       <c r="R22" t="n">
-        <v>6346007</v>
+        <v>6346117</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,12 +2978,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Med tall.  Artbestämning konfirmerad efter DNA sekvensering.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2998,22 +3008,22 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Julien Hach, Karin Hjelmér</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129352710</t>
+          <t>https://artportalen.se/Sighting/137144729</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129540854</v>
+        <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87262</v>
+        <v>87558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,37 +3031,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Byrum, Byrum, Öl</t>
+          <t>Bokhultet, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620133</v>
+        <v>620123</v>
       </c>
       <c r="R23" t="n">
-        <v>6346064</v>
+        <v>6346117</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3075,12 +3090,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Med gran.  Artbestämning konfirmerad efter DNA sekvensering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,7 +3111,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>mikroskoperad</t>
+          <t>barcode</t>
         </is>
       </c>
       <c r="AG23" t="b">
@@ -3105,22 +3125,22 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Julien Hach, Martin Peraic</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129540854</t>
+          <t>https://artportalen.se/Sighting/137144687</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137115511</v>
+        <v>129352710</v>
       </c>
       <c r="B24" t="n">
-        <v>87445</v>
+        <v>87204</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,41 +3148,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248956</v>
+        <v>248952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Saxmossen, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620130</v>
+        <v>620142</v>
       </c>
       <c r="R24" t="n">
-        <v>6346049</v>
+        <v>6346007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,22 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,76 +3216,68 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Peraic</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+          <t>Julien Hach, Karin Hjelmér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137115511</t>
+          <t>https://artportalen.se/Sighting/129352710</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137127987</v>
+        <v>129540854</v>
       </c>
       <c r="B25" t="n">
-        <v>87506</v>
+        <v>87262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>249228</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Saxmossen, Öl</t>
+          <t>Byrum, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620130</v>
+        <v>620133</v>
       </c>
       <c r="R25" t="n">
-        <v>6346049</v>
+        <v>6346064</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,22 +3304,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,34 +3318,38 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Peraic</t>
+          <t>Julien Hach</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+          <t>Julien Hach, Martin Peraic</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137127987</t>
+          <t>https://artportalen.se/Sighting/129540854</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137127949</v>
+        <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87557</v>
+        <v>87451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,26 +3357,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6052416</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3402,7 +3391,7 @@
         <v>620130</v>
       </c>
       <c r="R26" t="n">
-        <v>6346057</v>
+        <v>6346049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,7 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,6 +3459,246 @@
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137115511</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137127987</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87512</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>620130</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6346049</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137127987</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137127949</v>
+      </c>
+      <c r="B28" t="n">
+        <v>87563</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Saxmossen, Öl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>620130</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6346057</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Peraic</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Peraic, Julien Hach, Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137127949</t>
         </is>
@@ -3502,6 +3731,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87379</v>
+        <v>87383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87411</v>
+        <v>87415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87411</v>
+        <v>87415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87512</v>
+        <v>87516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87563</v>
+        <v>87567</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87383</v>
+        <v>87385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87415</v>
+        <v>87417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87415</v>
+        <v>87417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87516</v>
+        <v>87518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87567</v>
+        <v>87569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87385</v>
+        <v>87398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87417</v>
+        <v>87430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87417</v>
+        <v>87430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87518</v>
+        <v>87531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87569</v>
+        <v>87582</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87398</v>
+        <v>87400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87430</v>
+        <v>87432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87430</v>
+        <v>87432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87531</v>
+        <v>87533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87582</v>
+        <v>87584</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87400</v>
+        <v>87403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87432</v>
+        <v>87435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87432</v>
+        <v>87435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87584</v>
+        <v>87587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87403</v>
+        <v>87413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87435</v>
+        <v>87445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87435</v>
+        <v>87445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87536</v>
+        <v>87546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87587</v>
+        <v>87597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87445</v>
+        <v>87446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87445</v>
+        <v>87446</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87597</v>
+        <v>87598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87446</v>
+        <v>87449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87446</v>
+        <v>87449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87547</v>
+        <v>87550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87598</v>
+        <v>87601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87417</v>
+        <v>87422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87449</v>
+        <v>87454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87449</v>
+        <v>87454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87550</v>
+        <v>87555</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87601</v>
+        <v>87606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87422</v>
+        <v>87433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87454</v>
+        <v>87465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87454</v>
+        <v>87465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87555</v>
+        <v>87566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87433</v>
+        <v>87434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87465</v>
+        <v>87466</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87465</v>
+        <v>87466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87566</v>
+        <v>87567</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87434</v>
+        <v>87437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87466</v>
+        <v>87469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87466</v>
+        <v>87469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87567</v>
+        <v>87570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 34948-2022 artfynd.xlsx
+++ b/artfynd/A 34948-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137115600</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137116492</v>
       </c>
       <c r="B10" t="n">
-        <v>87437</v>
+        <v>87441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>137115228</v>
       </c>
       <c r="B14" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>137115221</v>
       </c>
       <c r="B21" t="n">
-        <v>87469</v>
+        <v>87473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>137144729</v>
       </c>
       <c r="B22" t="n">
-        <v>87469</v>
+        <v>87473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>137144687</v>
       </c>
       <c r="B23" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137115511</v>
       </c>
       <c r="B26" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>137127987</v>
       </c>
       <c r="B27" t="n">
-        <v>87570</v>
+        <v>87574</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137127949</v>
       </c>
       <c r="B28" t="n">
-        <v>87621</v>
+        <v>87625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
